--- a/光伏配储项目/电价数据/2026/珠海A厂.xlsx
+++ b/光伏配储项目/电价数据/2026/珠海A厂.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.55448</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38009</v>
+      </c>
+      <c r="C117" t="n">
+        <v>1.72435</v>
+      </c>
+      <c r="D117" t="n">
+        <v>1.17442</v>
+      </c>
+      <c r="E117" t="n">
+        <v>1.18515</v>
+      </c>
+      <c r="F117" t="n">
+        <v>1.22261</v>
+      </c>
+      <c r="G117" t="n">
+        <v>1.23372</v>
+      </c>
+      <c r="H117" t="n">
+        <v>1.16881</v>
+      </c>
+      <c r="I117" t="n">
+        <v>1.16918</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.44107</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.72763</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.78085</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.71317</v>
+      </c>
+      <c r="N117" t="n">
+        <v>1.16772</v>
+      </c>
+      <c r="O117" t="n">
+        <v>1.16773</v>
+      </c>
+      <c r="P117" t="n">
+        <v>1.16735</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.7064900000000001</v>
+      </c>
+      <c r="R117" t="n">
+        <v>1.1684</v>
+      </c>
+      <c r="S117" t="n">
+        <v>1.16803</v>
+      </c>
+      <c r="T117" t="n">
+        <v>1.16661</v>
+      </c>
+      <c r="U117" t="n">
+        <v>1.16759</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.7605</v>
+      </c>
+      <c r="W117" t="n">
+        <v>1.16814</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39496</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.7353999999999999</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>1.16806</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>1.1722</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.77859</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>1.19669</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>1.27877</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.32442</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.32883</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.3405</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.4041</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.87627</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.68841</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.68467</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.31347</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.46425</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.7504700000000001</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.77371</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.40439</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.38745</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>1.03757</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>1.02279</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>1.11539</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.7605</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.32592</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.7175499999999999</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.51379</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.41058</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.40701</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.41052</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.7924099999999999</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.9730800000000001</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>1.34184</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.5322</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.77707</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.45178</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.785</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.7605</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.98323</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.914</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>1.06989</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>1.34119</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>1.16856</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>1.18678</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.7432000000000001</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.23216</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>1.18681</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>1.10591</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>1.24738</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>1.54566</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>1.25048</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.27053</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>1.4951</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>1.32598</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>1.25425</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>1.44195</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>1.37201</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>1.30269</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.81237</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47986</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.4104100000000001</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41279</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.422</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="C118" t="n">
+        <v>1.18278</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>1.04983</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>1.18333</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.53767</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.52274</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.5064</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.5143300000000001</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.80322</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.70427</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.77749</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.68298</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38099</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39205</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.6755099999999999</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.7956299999999999</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.7404500000000001</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.7408400000000001</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.7408400000000001</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.7404500000000001</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.72241</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.78455</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>1.0884</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>1.44873</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>1.03643</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.781</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.6762899999999999</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.74191</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.64255</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.64455</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.95086</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>1.16622</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.7898999999999999</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>1.13585</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>1.05222</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>1.00725</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.71709</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.5499400000000001</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.57199</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.68645</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>1.18774</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>1.24623</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>1.49274</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.31003</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>1.18679</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>1.66393</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>1.08887</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.8331499999999999</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>1.2619</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>1.15866</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>1.29003</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.31338</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.62473</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.63858</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.56611</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.6192799999999999</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>1.18766</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>1.18678</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>1.18676</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>1.18779</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.99395</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>1.18676</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.18707</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.18459</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.68108</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>1.18706</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.213</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.24341</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.54164</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.44872</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.18705</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>1.51141</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>1.27124</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.7470399999999999</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.7627699999999999</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.9204199999999999</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.4401</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43408</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.3377</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37686</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35415</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33631</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.3214</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.74421</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.9398</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.89061</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.64538</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.7433200000000001</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.6444800000000001</v>
+      </c>
+      <c r="I119" t="n">
+        <v>1.55958</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.93628</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.93632</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.8870399999999999</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.7605</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.93775</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.73994</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.9358099999999999</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.64371</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37075</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35988</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36547</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35639</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.37245</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.36337</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.39154</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39644</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.74324</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.6451</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.74251</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.7402000000000001</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.70431</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.7403</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.7407100000000001</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.65603</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.70212</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.84066</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>1.11848</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.89986</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.7656499999999999</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.7266900000000001</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.6400800000000001</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.3308</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.33299</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.34495</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.6500199999999999</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.43842</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.7605</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>1.1868</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>1.55633</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.72593</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>1.19786</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>1.65382</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>1.1951</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>1.18674</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.7979700000000001</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.95813</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>1.18678</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>1.18677</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.90328</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.56313</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.42093</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.47771</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.6791200000000001</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>1.18772</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>1.04454</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>1.18679</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>1.42379</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>1.25775</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>1.18679</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>1.21836</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>1.21352</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>1.42715</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>1.27845</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>1.29949</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>1.66877</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>1.1966</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>1.199</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>1.05928</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>1.09467</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>1.11578</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>1.10177</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>1.22669</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>1.18679</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>1.27048</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>1.01285</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.76425</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.72081</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.53537</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.41317</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.3432</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="C120" t="n">
+        <v>1.18967</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.9422999999999999</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.93208</v>
+      </c>
+      <c r="F120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.89289</v>
+      </c>
+      <c r="H120" t="n">
+        <v>1.06371</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.74879</v>
+      </c>
+      <c r="J120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="K120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.88814</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.7605</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.97629</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.93598</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.88615</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.74103</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.74076</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.54461</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.6426799999999999</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.54459</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.3292</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.5466</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.7605</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.7412000000000001</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.8875</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.74019</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.68548</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.64264</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.54774</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.68376</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.72654</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.93996</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>1.18677</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>1.18798</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.85337</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>1.57246</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>1.66595</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.90452</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.8814500000000001</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>1.16125</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>1.42718</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>1.77353</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.97154</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>1.23084</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.6964199999999999</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>1.12216</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.5241399999999999</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.48732</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.65818</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>1.00114</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>1.10977</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>1.25898</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>1.18673</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>1.08457</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>1.00229</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>1.03504</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.99901</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>1.2955</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>1.47636</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.81426</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>1.37914</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>1.23387</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.8659</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>1.1065</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>1.18655</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>1.1342</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>1.18922</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>1.28595</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>1.34655</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>1.18921</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>1.29973</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>1.20422</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>1.19316</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>1.1871</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>1.2165</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>1.22834</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>1.21402</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>1.18944</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>1.18787</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.7400399999999999</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.52943</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.33574</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.74963</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.33203</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.32956</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.3405</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.3405</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.32176</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.7498899999999999</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.49526</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.40137</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36257</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.3432</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.3432</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.3432</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.3432</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.3426</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.3426</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.3426</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.3426</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.3426</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.3426</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.3405</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.3405</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.3405</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.3405</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.3405</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.3405</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.3405</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.3405</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.3405</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.3405</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.3426</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.3405</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3405</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.3405</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.33414</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.33877</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.48046</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.51063</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.52624</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.40408</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.31526</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.46213</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.33343</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.43141</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.46128</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.72335</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.85662</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.61961</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.70802</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.34028</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.73287</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.33289</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.85662</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.7132000000000001</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.33343</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.55443</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.55443</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.5450700000000001</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.59876</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.478</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.1018</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.3305</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.30446</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.28865</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.28598</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.31457</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.3334</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>0.33394</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.5518999999999999</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.48651</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.5189</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.46912</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.64971</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.51288</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.49194</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.40375</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.49746</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.49768</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.6150599999999999</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.40868</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.51567</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.51462</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.41175</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.49227</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.35525</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.41094</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46752</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.37964</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39642</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.40454</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35808</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35523</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.34428</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="C122" t="n">
+        <v>1.21433</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.99646</v>
+      </c>
+      <c r="E122" t="n">
+        <v>1.01155</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.59922</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.72123</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.36489</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="N122" t="n">
+        <v>1.16765</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.34184</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33991</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.33764</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.33845</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.33764</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33531</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.33877</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.3424</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.27825</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.07490999999999999</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>0.30657</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04711</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04874</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.03979</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.26957</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.07831</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.28969</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.12425</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.00371</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>0.30257</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.30057</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.30457</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>0.26266</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>0.28723</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>0.34459</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>0.29249</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>0.296</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.36126</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.39133</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.43072</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.36615</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.36666</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.35825</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.35764</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.45048</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.36373</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.39445</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.3896</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.36486</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.39461</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.3585</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.34079</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.36738</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.39734</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.36439</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.3673</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36593</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33413</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.76271</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.69067</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40508</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.34402</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.3204</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.31054</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31964</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.31209</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.31018</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.27696</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.30641</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.30474</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.30842</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.30369</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.30242</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.30641</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.28789</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.28449</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.1686</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14582</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15718</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15646</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.2327</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.2119</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.29112</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.2729</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.30641</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.30965</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.31641</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.31018</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.31369</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.31365</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.30305</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.32042</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.3224</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.3279</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.33606</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.39017</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.7663</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.90322</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.69967</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.69967</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.7055900000000001</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.76993</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.9805499999999999</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.44833</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.36804</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.49586</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.75787</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.7496900000000001</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.9213899999999999</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.69768</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.54686</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.48514</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.45666</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.09403</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.30633</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.32475</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.38043</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.30688</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.38043</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.74976</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.74961</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.6497200000000001</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.61168</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.48068</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.73991</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.6107100000000001</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.7543</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>1.03076</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>1.43122</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.8610800000000001</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>1.46209</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>1.35123</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.8159500000000001</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>1.41012</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>1.0657</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>1.42852</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.7918</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.46794</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.80431</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5303</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.78816</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.87899</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.88086</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.50566</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.41511</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.41575</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.46413</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.22286</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87899</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.5511200000000001</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.6430800000000001</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.54215</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.8067799999999999</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.69808</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.65899</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.64388</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.66983</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38723</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41476</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43375</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34386</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.7554</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.6606000000000001</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.64388</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.60039</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.43719</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59596</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.56449</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.66879</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>1.07786</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.6560499999999999</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.52939</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.57672</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>1.5965</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.9655</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>1.339</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.30779</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>1.28152</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.57076</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.80003</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.57768</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.65628</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.55826</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>1.01521</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.7357</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.6442</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.5831799999999999</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>1.01354</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>1.15217</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.56236</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.74699</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.74376</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.69725</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.74694</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.89289</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.7460599999999999</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.74693</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.60984</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.59353</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.74683</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.7845299999999999</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.79875</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.80223</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.65865</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.9511799999999999</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.35979</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.74324</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.93665</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.8893</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.9395</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.77726</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.77726</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.6922200000000001</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.74126</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.37547</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.35502</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.36821</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35864</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.64388</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.39154</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.3504</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.371</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.3153</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33456</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.66432</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.41175</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.53291</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.62951</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.7496</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.89949</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>1.15322</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.9408</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.56064</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>1.12571</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.86803</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.97576</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.88537</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.65424</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.83828</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>1.09725</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.74351</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.53439</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.40334</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.38457</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.37605</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.89949</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>1.2045</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.9358500000000001</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>1.23412</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.80771</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.8389</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.9421900000000001</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.7605</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.34749</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.33414</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.40807</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.39333</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.35236</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.37637</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.3284</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.47802</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.39756</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.38562</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.36526</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.44485</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.38332</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.34446</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.37112</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.35041</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.39762</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.50057</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.43244</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.42042</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.35391</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.41589</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44782</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.34461</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.4204</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35895</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40168</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.4004</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59663</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C126" t="n">
+        <v>1.2005</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.51586</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.7027</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.79415</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.6489400000000001</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.5828300000000001</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.43956</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43711</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41476</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43375</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43375</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.3902</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42768</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39608</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43375</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.4020899999999999</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.73305</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.4279</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.7605</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>1.18059</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.92441</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.65888</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.71168</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>1.56306</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>1.60236</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>1.11454</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>1.6152</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.9049400000000001</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.5996</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>1.48168</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>1.45621</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>1.42182</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>1.421</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>1.77664</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>1.01378</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>1.53797</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.3432</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.59616</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.86691</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>1.52889</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.7605</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>1.07599</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>1.09756</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.95366</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.99761</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.94977</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>1.18678</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>1.18647</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.8901699999999999</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>1.18649</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>1.63236</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.99875</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>1.04286</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>1.18648</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.97939</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>1.02032</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>1.5809</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.94348</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>1.00878</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>1.06417</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.9138500000000001</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.8930399999999999</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>1.68606</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>1.12619</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>1.6143</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.98817</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>1.02541</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.7605</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.3869</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.34125</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.3432</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3193</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.8886900000000001</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.73997</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.7400800000000001</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.3432</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.3432</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.3432</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.3426</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.3426</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.3426</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.3426</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.3426</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.3432</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.3426</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.3426</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.3405</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.3426</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.3426</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.69614</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.3251</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.339</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.594</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.3323</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.3201</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.74322</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33995</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.38745</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.35871</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.93579</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.73997</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.69124</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.7399199999999999</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.69163</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.3104</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.74136</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>0.41726</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.30969</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.8862599999999999</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.7605</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>1.15016</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>1.44725</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.7605</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.7605</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.7602300000000001</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.7004900000000001</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.69216</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.7605</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.88887</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.8862899999999999</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.7605</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.6414800000000001</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.63087</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.6444099999999999</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.6495</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.37197</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.6992200000000001</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.37871</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.40289</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.36032</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.393</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34365</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.34648</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.6938799999999999</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.6926599999999999</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39374</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.4020899999999999</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39799</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.45673</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.43939</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44431</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44431</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.6927300000000001</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.6954</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.6926100000000001</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.3923</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34932</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.59829</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.5460700000000001</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46858</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.4237</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41597</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38099</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.3802</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.59493</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.88727</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.78947</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.78972</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.78923</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.80833</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.69192</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.73607</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.5938099999999999</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.49608</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.59376</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.49608</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.7605</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.79886</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.7894800000000001</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.7605</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.69167</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.6911900000000001</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.6446000000000001</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32657</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34491</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.33443</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.32637</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.3405</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.32636</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.33148</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.59312</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.32822</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.3426</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.39099</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.33267</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.30876</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.29637</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.3104</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.3164</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31638</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.32918</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.48364</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.3419</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.34173</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.32491</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.35989</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.33962</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.36875</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.3757799999999999</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.34742</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.4126</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.48871</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.6999500000000001</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.60042</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.6266699999999999</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.85022</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>1.2679</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>1.16542</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.85022</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.45028</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.39642</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.4297</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.70002</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.95021</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>1.18387</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>1.13268</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.55001</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.4388</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.42916</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.39708</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.37946</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41962</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.39127</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.4978</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.44696</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.41427</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.42573</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36624</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.4201</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37043</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.5660299999999999</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.3808</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.3508</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34932</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.35995</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.6404099999999999</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.63822</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.6404099999999999</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.59513</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.7605</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.49703</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.59509</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.49696</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.5952200000000001</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.66375</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.7605</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.68696</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.7605</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>1.12358</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>1.46561</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.4141</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>1.30113</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>1.00036</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.9887400000000001</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.98966</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>1.56049</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>1.55677</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.9430299999999999</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>1.10055</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>1.79399</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>1.65878</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>1.64878</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>1.73749</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.8087300000000001</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>1.29215</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.32836</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.7605</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>1.3503</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.48388</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>1.15704</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.98365</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>1.64878</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>1.63378</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>1.6665</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>1.67886</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>1.67394</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>1.65071</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>1.67378</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>1.2068</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>1.70891</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>1.78931</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>1.70526</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>1.71362</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>1.72102</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>1.64018</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>1.75531</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>1.01901</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>1.12832</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>1.69998</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>1.70762</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>1.70201</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>1.7863</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>1.73114</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.8202200000000001</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.67114</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.46521</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>1.26861</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.64619</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.7605</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.6355599999999999</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.66895</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.34419</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.33381</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.6304999999999999</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.78166</v>
+      </c>
+      <c r="E130" t="n">
+        <v>1.3658</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.6560199999999999</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.7605</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.39213</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.35498</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.66801</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.63974</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.79579</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.7605</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.7605</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.65944</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.3432</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.3432</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.3426</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.3426</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.3426</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.62109</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.3432</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34492</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33991</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.3348</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.35008</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.3974</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.40248</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.42764</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.75342</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.49529</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.5135599999999999</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.52219</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.33975</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34858</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.34489</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32843</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28467</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.33977</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.33963</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32713</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.33977</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.3284</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.34365</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.3426</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.32839</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.34457</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.33606</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.40807</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.45342</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.93021</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>1.48441</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>1.1897</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.9002100000000001</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.76627</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.44958</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.39541</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.45696</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.49997</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.45037</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.49002</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37155</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39154</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37155</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.4020899999999999</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35494</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.38099</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34925</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35194</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.35606</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35547</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.3508</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.3468</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.38944</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34757</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33695</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.3432</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.3426</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.3426</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.3426</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.3426</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33622</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.3367</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.3426</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.40565</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.40599</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.34468</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.62105</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.41849</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.3432</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.38884</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.3432</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.3432</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.3264</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.3432</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.38977</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.3432</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.44997</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.75346</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.42957</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.51802</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>1.70449</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.49997</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.40732</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.41998</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.42847</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.35502</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.3323</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.42416</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.56631</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.38955</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35441</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.42612</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.45499</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35222</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.40133</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36203</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.6635599999999999</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.44999</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.44602</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.37782</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40107</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.38387</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.37673</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.6411</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.81696</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.46781</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.39126</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.44708</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.38212</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35206</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.345</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.70277</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.66738</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.66234</v>
+      </c>
+      <c r="F132" t="n">
+        <v>1.24912</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.65067</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.57175</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.53173</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.46016</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.48779</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.45705</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.3535</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36055</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36068</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35691</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35227</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35965</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.36001</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35968</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.34001</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.3706</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.3587</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35641</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36578</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35641</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35641</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35169</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35849</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.37615</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.4387</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.51605</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.42001</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.55162</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.7605</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.36077</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.76607</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.33201</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.34596</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.3439</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.27882</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.33835</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.48307</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.33809</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.3432</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.34031</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.39401</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.54391</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.5007699999999999</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.35424</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.36079</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.73546</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.7605</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.55264</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.50076</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.45001</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>1.01757</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>1.48168</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>1.45516</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>1.10388</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>1.13304</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>1.09137</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.39169</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>1.12095</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>1.13816</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>1.02711</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>1.20254</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>1.15043</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>1.13835</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>1.19413</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.85092</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>1.19887</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.85575</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>1.353</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.9006900000000001</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>1.71161</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.75285</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.96182</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>1.58296</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.72135</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.71105</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.7897799999999999</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.61026</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36717</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36002</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.7605</v>
+      </c>
+      <c r="D133" t="n">
+        <v>1.41424</v>
+      </c>
+      <c r="E133" t="n">
+        <v>1.74084</v>
+      </c>
+      <c r="F133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.42819</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.69698</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.94111</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.92983</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.7095</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.69165</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.86497</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.88062</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.88662</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.71474</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.90746</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.7128300000000001</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.87826</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.6464800000000001</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.5764400000000001</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.5805499999999999</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.5805499999999999</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.64815</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.47752</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.5765800000000001</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.46921</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.7618200000000001</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.62266</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.5768</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.87337</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.65638</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>1.10953</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>1.79513</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.39913</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.7605</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>1.29747</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>1.35869</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>1.7372</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>1.66229</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>1.36755</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>1.0036</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>1.60907</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.49996</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.49997</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.55092</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.59948</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.75105</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>1.20038</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.7055499999999999</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.93789</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.6811200000000001</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.9595499999999999</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.8989</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>1.76315</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>1.73288</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>1.18382</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>1.18732</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>1.44928</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>1.26656</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>1.67069</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>1.25205</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>1.29731</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>1.11453</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>1.43875</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>1.04505</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.97188</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.90773</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.44945</v>
+      </c>
+      <c r="C134" t="n">
+        <v>1.34501</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.69825</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.49923</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.58245</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.47899</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42848</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.4016</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40804</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38922</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.3801</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.3568</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36578</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.3758</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.371</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36578</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38688</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.3666</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36156</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35522</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.44999</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.48728</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.40569</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.5320900000000001</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.3956</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38688</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.3515</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.37105</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.5336900000000001</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.7982400000000001</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.6831900000000001</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.65561</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>1.50405</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>1.08474</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>1.69164</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>1.66465</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.8067799999999999</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>1.08083</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>1.19368</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.49999</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>1.19364</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.5430199999999999</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>1.15395</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.55459</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.5648500000000001</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.49995</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.23291</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.33932</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.32221</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.31797</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.37339</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34986</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.42909</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.48078</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.50001</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.45079</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.35304</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.38343</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.5222</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.51735</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.60076</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.37506</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.38084</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.39214</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.3785</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38141</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.7605</v>
+      </c>
+      <c r="D135" t="n">
+        <v>1.13914</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.87049</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.7605</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.4984</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.44871</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.41869</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.39851</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35844</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.34919</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.35599</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34483</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.39911</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.39999</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.3432</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.33667</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.33667</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.38055</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.3426</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.3405</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.33951</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.3284</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.41996</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.34732</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.33764</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.3395899999999999</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.35246</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.42092</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.3432</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.33884</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.44994</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.39783</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.34868</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.4999</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.32562</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04325</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.36751</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.3426</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.32736</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.33676</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.32285</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.33933</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.46114</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.3430299999999999</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.3434</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.34213</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.34344</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.34399</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.44997</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.34436</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.39999</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.38017</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.40085</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.41885</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.44998</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.59429</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.48366</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.46249</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.39999</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.46342</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.44998</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.46088</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.34441</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.5530900000000001</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.38783</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.44998</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.42085</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.3938</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.40879</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.3767</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.46115</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.41999</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.46933</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.6938</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.65665</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.6610499999999999</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.67923</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.64105</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.49719</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.44813</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.39906</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.3991</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="C136" t="n">
+        <v>1.04738</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.497</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.69352</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.49715</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.49767</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.62205</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.61615</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.61105</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.61105</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.3432</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.3432</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.3432</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.3432</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.3432</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.3432</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.3426</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.3426</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.3405</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.3426</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.3426</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.3426</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.3426</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.3426</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.3426</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.3426</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.3426</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.37228</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.38218</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.23381</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.30752</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.27224</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.38865</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.38835</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>0.32614</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.30044</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.3063</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>0.3426</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>0.3162</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>0.15336</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>0.7370599999999999</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>0.21466</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>0.38751</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>0.30147</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>0.27308</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>0.14019</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>0.44727</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.3426</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>0.39843</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>0.35427</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.69985</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.5756599999999999</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>0.30626</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>0.32017</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>0.30626</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>0.30764</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>0.32216</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>0.49989</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>0.38757</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.38848</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.392</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.7605</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.36646</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.39252</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.3536</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.36731</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.38298</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.39998</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.37206</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.39998</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.38288</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.44805</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.44891</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.44873</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.39984</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.3931</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.38305</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.39315</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.38252</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.42888</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.80823</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.38361</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.46788</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.39318</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.38922</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.38917</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.3859</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.40261</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.37097</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.49039</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.31035</v>
+      </c>
+      <c r="C137" t="n">
+        <v>1.10195</v>
+      </c>
+      <c r="D137" t="n">
+        <v>1.38434</v>
+      </c>
+      <c r="E137" t="n">
+        <v>1.1874</v>
+      </c>
+      <c r="F137" t="n">
+        <v>1.0773</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.52549</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.7605</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.7605</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.51512</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.4171</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.42949</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.42663</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.40865</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.41583</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.39449</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.38772</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.4448</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.55804</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.35912</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.42605</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.38775</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.4436</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.6896</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>1.28294</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.42477</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.7605</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.80536</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.45459</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.40336</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.7605</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.41122</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.52888</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>1.47134</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>1.47573</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>1.24368</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>1.08814</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.9865</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>1.31668</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.63591</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.5499299999999999</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.38891</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.49735</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.58316</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.7605</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.55089</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.5498999999999999</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.39704</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.22582</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.33196</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.7605</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.7605</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.58439</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.45107</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.3222</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.49836</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>1.01284</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.7709600000000001</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.62814</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.7605</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>1.20456</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.6089</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.75112</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.63952</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>1.26792</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.90155</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.8859400000000001</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.90635</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.9248200000000001</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>1.17656</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.651</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.9595900000000001</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.6946</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.98546</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>1.65844</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>1.67896</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>1.75911</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>1.65844</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>1.26484</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>1.04534</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>1.02634</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>1.03524</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>1.54796</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>1.36406</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>1.05776</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.41086</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.38172</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.7605</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.39017</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.3455</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.5592200000000001</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.8085</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.54996</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.7582100000000001</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.7605</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.56175</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.47046</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.45984</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.4083</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.42906</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.41999</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.35832</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.37079</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.35497</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34818</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.38228</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.36734</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.35765</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.35121</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.35947</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.38164</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.41998</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.40324</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.42648</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.63722</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.59593</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.5619299999999999</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.54323</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.45253</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.4815</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.49993</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.56051</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.81709</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>1.17486</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>1.1405</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>1.05149</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>1.15299</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>1.75617</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>1.74511</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>1.05992</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>1.08387</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.68426</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.55502</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.5615599999999999</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.5615599999999999</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.47996</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.30674</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.48427</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.34865</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.54995</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.55001</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.5463</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.6618200000000001</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>1.55619</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>1.05199</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.66199</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.54995</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.49996</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.49996</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.48259</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.49996</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.48244</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.49997</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.57833</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.55783</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.56174</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.49997</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.51419</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.40339</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.40021</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.38451</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.42346</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.50171</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.56175</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.6618099999999999</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>1.17552</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>1.0779</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.6617799999999999</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.5827899999999999</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>1.17563</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.87194</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.6617999999999999</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>1.16178</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.83929</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.49997</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.51196</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.49997</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.4404</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.53553</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.39164</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.39963</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.34958</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.34476</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.36934</v>
+      </c>
+      <c r="D139" t="n">
+        <v>1.05253</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.7615599999999999</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.7692</v>
+      </c>
+      <c r="G139" t="n">
+        <v>1.18502</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.7605</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.49856</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.41892</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.39991</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.41998</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.41926</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.35808</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.39317</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.3549</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.35382</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.37921</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.36412</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.36261</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.35169</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34629</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.35391</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.35023</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.36222</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.3432</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.369</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.36205</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.38679</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35914</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.62995</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.58951</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.42691</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.64232</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>1.03894</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>1.26937</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.93592</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.9867</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>1.03455</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.9774700000000001</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.94497</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.97548</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.95845</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.94309</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.95304</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.47765</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.87874</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>1.23187</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.7605</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>1.22821</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>1.31343</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>1.2949</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.72856</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.9485399999999999</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.8686699999999999</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.93584</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>1.5499</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>1.17802</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>1.75231</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>1.70375</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>1.56446</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>1.2768</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>1.70926</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.6725599999999999</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.7605</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.7605</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.57443</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.5532899999999999</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.37942</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.3432</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.3432</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.7069800000000001</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.42426</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.54937</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.40528</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.46029</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.69329</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.38054</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.7416</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.6999099999999999</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.41518</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.3726</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.373</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.369</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.7605</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.3903</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.3806</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37385</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37849</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.3766</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36872</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36659</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36112</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.3596</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.3603</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35576</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.3288</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35607</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35095</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.3471</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37113</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.37585</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.36468</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.4037</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.38907</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.36728</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.7105</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.46668</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.75026</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.52446</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.51087</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.44377</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>1.02434</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.92257</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>1.03488</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.93288</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>1.05288</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>1.03188</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>1.02988</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.31722</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>1.3817</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>1.09587</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>1.30714</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.66325</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.389</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.35965</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.6812</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.3568</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.62421</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.73661</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.72162</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>1.0227</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>1.72232</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>1.77373</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>1.14552</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>1.43225</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>1.65084</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>1.41928</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>1.57526</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>1.16812</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>1.61474</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>1.5735</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>1.64605</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>1.64669</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39893</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.8145800000000001</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.7695299999999999</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.80913</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.8091699999999999</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.3756</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.26742</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.49704</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.38853</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.37057</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.36792</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.3554</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.35937</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.7605</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.35965</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.34983</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.43999</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.43846</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.3795</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.37975</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.35925</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.35874</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.35935</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.36086</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.36742</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.35918</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.35767</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.3813</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.35946</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.37296</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.49996</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.37706</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.35622</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.35026</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.35873</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.34329</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.38182</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.7605</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.45179</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.3768</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.40379</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.48628</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.61527</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.3432</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.32228</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.3432</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.3432</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>1.21197</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>1.21464</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>1.15086</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.51866</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.32858</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.7012200000000001</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>1.09162</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.48324</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.3426</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.42767</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.3432</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.3432</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.3432</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.3182</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.3405</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.3405</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.3405</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.31962</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.41723</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.41741</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.41664</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.48536</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>1.0668</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.5643400000000001</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>1.04709</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>1.05899</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>1.17493</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.6113200000000001</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.41327</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>1.19631</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>1.29772</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.61793</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.46581</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>1.11789</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>1.09935</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.3426</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.3426</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.64149</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>1.17488</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.34142</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.3426</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.3426</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.3426</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.3426</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.3426</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.3405</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.3405</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.35051</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.00175</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.7605</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.7605</v>
+      </c>
+      <c r="F142" t="n">
+        <v>1.52212</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.5155</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.48164</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.5202</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.5408999999999999</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.39859</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.4907</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.4907</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.5202</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.5408999999999999</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.5202</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.39322</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.38495</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.5307999999999999</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.5202</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.5202</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.5202</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.5202</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.5107</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.4958</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.4958</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.4907</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.4907</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.37232</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.84792</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.4907</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.37421</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.35499</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.36024</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.4958</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.4958</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.4958</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.4958</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.5202</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.5307999999999999</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.40857</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>1.38279</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.6223099999999999</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.75814</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.89739</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.88661</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.91584</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.9979199999999999</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.71316</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.4958</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.42616</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.18225</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.15648</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.96135</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.29924</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.36654</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.6722400000000001</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.25204</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.4958</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.4958</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.4958</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.4806</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.4907</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.4958</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.5107</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.4958</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.4958</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.62917</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>1.62801</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>1.41491</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.4958</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.5107</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.5107</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.5307999999999999</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.5408999999999999</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.515</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.6293800000000001</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.53506</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.5202</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.5508</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.5508</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.5408999999999999</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.5408999999999999</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.7605</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.5508</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.5408999999999999</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.6428700000000001</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.53311</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.5508</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.5508</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.5508</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.5508</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.5408999999999999</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.3807</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.6008</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.6008</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.5308999999999999</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.5308999999999999</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.5308999999999999</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.5152599999999999</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.55343</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.41936</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.5207999999999999</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.5008</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.37304</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.45944</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.45943</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.33339</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.3807</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.33406</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.3594</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.35001</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36426</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.3606</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.43854</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.3807</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.41224</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.49509</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.5477000000000001</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.5207999999999999</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.5207999999999999</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.5207999999999999</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.5343600000000001</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.5207999999999999</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.94265</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>1.33558</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.6204</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>1.5086</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.5207999999999999</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.5207999999999999</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.5207999999999999</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.5207999999999999</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.5207999999999999</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.50337</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.5207999999999999</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.54462</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.5308999999999999</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.5101600000000001</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.5207999999999999</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.6008</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.5207999999999999</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.5207999999999999</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.5207999999999999</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.5207999999999999</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.5207999999999999</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.5207999999999999</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.5207999999999999</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.5207999999999999</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.5207999999999999</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.5207999999999999</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.5207999999999999</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.5207999999999999</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.5207999999999999</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.5308999999999999</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.5342899999999999</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.5207999999999999</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.5207999999999999</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.5207999999999999</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.5308999999999999</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.3807</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.72589</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.8291000000000001</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.8084199999999999</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.6008</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.79901</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.74771</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.6102000000000001</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.6008</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.6008</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.62315</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.6275499999999999</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.6008</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.6008</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.6888200000000001</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.79963</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.69069</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.5998300000000001</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.5207999999999999</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.5008</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.3966</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.37241</v>
       </c>
     </row>
   </sheetData>
